--- a/Data/Home/Balcony.WashingMachine001.xlsx
+++ b/Data/Home/Balcony.WashingMachine001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709449744</v>
+        <v>1711875419</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709451244</v>
+        <v>1711877529</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709797541</v>
+        <v>1712052596</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709798970</v>
+        <v>1712055632</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709799822</v>
+        <v>1712217509</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709802055</v>
+        <v>1712220296</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1710056527</v>
+        <v>1712307609</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1710058897</v>
+        <v>1712309604</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1710320720</v>
+        <v>1712403785</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1710322732</v>
+        <v>1712405940</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1710405488</v>
+        <v>1712647595</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1710407573</v>
+        <v>1712650626</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1710490083</v>
+        <v>1712738542</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1710491377</v>
+        <v>1712741431</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1710740303</v>
+        <v>1712821603</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1710742769</v>
+        <v>1712824090</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1710926170</v>
+        <v>1713012069</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1710927777</v>
+        <v>1713015173</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1711177659</v>
+        <v>1713178688</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1711179063</v>
+        <v>1713181086</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1711629036</v>
+        <v>1713441492</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1711631282</v>
+        <v>1713443341</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,229 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WashingMachine_Operation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1713953685</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Balcony.WashingMachine001.state: on</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WashingMachine_Operation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1713956294</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Balcony.WashingMachine001.state: off</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WashingMachine_Operation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1714131275</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Balcony.WashingMachine001.state: on</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WashingMachine_Operation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1714134008</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Balcony.WashingMachine001.state: off</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WashingMachine_Operation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1714221303</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Balcony.WashingMachine001.state: on</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WashingMachine_Operation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1714224079</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Balcony.WashingMachine001.state: off</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
